--- a/data/output/evaluasi_21.xlsx
+++ b/data/output/evaluasi_21.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="2100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2102" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2171" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2104" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2105" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2172" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2102" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2171" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2101" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2172" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2103" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2105" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2104" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +482,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-22.71181925883208</v>
+        <v>-23.94266136859186</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -490,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -505,20 +506,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-8.704043863037256</v>
+        <v>-22.35266536587673</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -537,16 +538,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.00573968180182</v>
+        <v>-9.732465633524754</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -561,20 +562,832 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.84189575241564</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>-0.03760732767831065</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pdrb_q2-25 vs implisit_q-to-q_pdrb_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth berlawanan arah</t>
+      <c r="D6" t="n">
+        <v>3.462578276061267</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.585801897695671</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3691066956953679</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.543306058991005</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20.02588419091514</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.181479762625322</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q1-25 vs q-to-q_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.226803256489171</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.354455527154037</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q1-25 vs y-on-y_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>21</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.064530189028845</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.422370594198874</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7.832567410977045</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.875146139728064</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.314813857918239</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-16.17739283386913</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-6.391985948852719</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.720153348001667</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9.965423565492362</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4.354455527154037</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q1-25 vs c-to-c_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.422370594198874</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2.538228229028644</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2.651642579030594</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3.314813857918239</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-8.315629955368564</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-7.626324171874731</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4.720153348001667</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>21</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.471813596364487</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2.85874214066485</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3.267337113512508</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>21</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kepulauan Riau</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.7709514839286177</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
         </is>
       </c>
     </row>
@@ -589,7 +1402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,11 +1439,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -639,380 +1452,296 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>243385.7951</v>
+        <v>-3.567538235559898</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pkp_q1-25_ril vs adhb_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-53312.1905896553</v>
+        <v>4.802230608928744</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-296997.2026941343</v>
+        <v>2.363942057528039</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-31985.2036692956</v>
+        <v>10.78774879450955</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-169746.5977213006</v>
+        <v>8.436488916526983</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.207860962607891</v>
+        <v>11.33925513991368</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>distribusi_pkp_q1-25_ril vs distribusi_pkp_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Distribusi revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.6754651919792067</v>
+        <v>6.696458468788324</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.6754651919792067</v>
+        <v>16.35281315294596</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-5.902275478997584</v>
+        <v>10.14293025355803</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.473810836982439</v>
+        <v>14.67175847285213</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kabupaten Karimun</t>
+          <t>Kabupaten Bintan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.496645783567119</v>
+        <v>-4.437150556507389</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>sog_q_pi_q3-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2101</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kabupaten Karimun</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.03850273577212025</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2101</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kabupaten Karimun</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.2946059583803396</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>2101</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kabupaten Karimun</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1.27252073303158</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,11 +1793,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1077,240 +1806,156 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-102064.37</v>
+        <v>-2.1458078857038</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-670236.3199999994</v>
+        <v>12.01640024131296</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-72333.01089000001</v>
+        <v>8.690907765010531</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-96955.11700000009</v>
+        <v>2.288912256794205</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.298204098150305</v>
+        <v>0.09000005829689642</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2102</v>
+        <v>2171</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Bintan</t>
+          <t>Kota Batam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.567538235516521</v>
+        <v>1.647107738910373</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2102</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Bintan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>7.600177649121355</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2102</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Bintan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-1.212019840443898</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2102</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Bintan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9592041412277729</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1362,197 +2007,225 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-409898.4148</v>
+        <v>3.122549473217682</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-194120.970051208</v>
+        <v>-2.186514461953403</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.286946794626793</v>
+        <v>-5.795014796120119</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.286946794626793</v>
+        <v>-2.193216452357297</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.7034390445142588</v>
+        <v>-8.669504064489487</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08181774277898896</v>
+        <v>-0.6517116041101852</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2171</v>
+        <v>2101</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kota Batam</t>
+          <t>Kabupaten Karimun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1972671685403972</v>
+        <v>0.4210125348055067</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2101</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Karimun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.424123927219386</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1567,7 +2240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1604,57 +2277,365 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2104</v>
+        <v>2172</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lingga</t>
+          <t>Kota Tanjung Pinang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.734359217960173</v>
+        <v>2.127425178870759</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2104</v>
+        <v>2172</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lingga</t>
+          <t>Kota Tanjung Pinang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1955136461923725</v>
+        <v>-3.48823577246134</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.981795407319396</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.521984064616225</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.615713608641198</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.252461963336468</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-11.66989123181303</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.644692471496078</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.48573783035305</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.032086164383913</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.07504011234998485</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.704592962404076</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2172</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.162431979623555</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1669,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1706,57 +2687,309 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Anambas</t>
+          <t>Kabupaten Natuna</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.2793528114421037</v>
+        <v>10.61542704107086</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2105</v>
+        <v>2103</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kepulauan Anambas</t>
+          <t>Kabupaten Natuna</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.271695300107908</v>
+        <v>-4.220000000000005</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1507883830076415</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12.25017376490463</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-12.99320276297277</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.865077501154372</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.19039738866167</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.498284498748991</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-12.52090084654585</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.092441313838551</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Natuna</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.9107185414041538</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1771,7 +3004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1808,29 +3041,523 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2172</v>
+        <v>2105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Tanjung Pinang</t>
+          <t>Kabupaten Kepulauan Anambas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.4254318638406207</v>
+        <v>10.0732904165655</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.8443687703902624</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.00021884089241</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>22.24671711027113</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.09503546372632742</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-11.62699550361526</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3.764076254081783</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.06344553287655</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-16.52681402523636</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.640048891444497</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1892484059425482</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.22671414905854</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-26.6218416639495</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.957725125284867</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-26.12550546466793</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.269055704207902</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lingga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1810196761237899</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_21.xlsx
+++ b/data/output/evaluasi_21.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
